--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55974A76-ACCE-4EEE-8FAE-8F68F7567405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F057E237-6D67-4189-9F73-35AFC9471591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="31935" yWindow="3675" windowWidth="19200" windowHeight="11205" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -4264,33 +4264,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
   <dimension ref="A1:C121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -4298,17 +4298,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20">
         <f>(1-EXP(-((C20/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21">
         <f t="shared" ref="B21:B84" si="0">(1-EXP(-((C21/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
         <v>2.9387164590499728E-6</v>
@@ -4367,7 +4367,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22">
         <f t="shared" si="0"/>
         <v>2.3508987656584158E-5</v>
@@ -4377,7 +4377,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B23">
         <f t="shared" si="0"/>
         <v>7.9336018158404631E-5</v>
@@ -4387,7 +4387,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" si="0"/>
         <v>1.8802429327882398E-4</v>
@@ -4397,7 +4397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="0"/>
         <v>3.6713369702505162E-4</v>
@@ -4407,7 +4407,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="0"/>
         <v>6.3414614007045462E-4</v>
@@ -4417,7 +4417,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="0"/>
         <v>1.006422790718059E-3</v>
@@ -4427,7 +4427,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" si="0"/>
         <v>1.5011520593627675E-3</v>
@@ -4437,7 +4437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="0"/>
         <v>2.1352885583158314E-3</v>
@@ -4447,7 +4447,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="0"/>
         <v>2.9254833434584626E-3</v>
@@ -4457,7 +4457,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="0"/>
         <v>3.8880058412656712E-3</v>
@@ -4467,7 +4467,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32">
         <f t="shared" si="0"/>
         <v>5.0386579732422526E-3</v>
@@ -4477,7 +4477,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33">
         <f t="shared" si="0"/>
         <v>6.3926811083940913E-3</v>
@@ -4487,7 +4487,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34">
         <f t="shared" si="0"/>
         <v>7.9646566013662247E-3</v>
@@ -4497,7 +4497,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35">
         <f t="shared" si="0"/>
         <v>9.7684008073131972E-3</v>
@@ -4507,7 +4507,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36">
         <f t="shared" si="0"/>
         <v>1.1816855602081967E-2</v>
@@ -4517,7 +4517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37">
         <f t="shared" si="0"/>
         <v>1.4121975575197189E-2</v>
@@ -4527,7 +4527,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38">
         <f t="shared" si="0"/>
         <v>1.6694613200417676E-2</v>
@@ -4537,7 +4537,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39">
         <f t="shared" si="0"/>
         <v>1.9544403420951564E-2</v>
@@ -4547,7 +4547,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40">
         <f t="shared" si="0"/>
         <v>2.267964921017894E-2</v>
@@ -4557,7 +4557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B41">
         <f t="shared" si="0"/>
         <v>2.6107209780122643E-2</v>
@@ -4567,7 +4567,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B42">
         <f t="shared" si="0"/>
         <v>2.9832393204970647E-2</v>
@@ -4577,7 +4577,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B43">
         <f t="shared" si="0"/>
         <v>3.3858855301670994E-2</v>
@@ -4587,7 +4587,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B44">
         <f t="shared" si="0"/>
         <v>3.8188506660006477E-2</v>
@@ -4597,7 +4597,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B45">
         <f t="shared" si="0"/>
         <v>4.2821429736777793E-2</v>
@@ -4607,7 +4607,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B46">
         <f t="shared" si="0"/>
         <v>4.7755807919210802E-2</v>
@@ -4617,7 +4617,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B47">
         <f t="shared" si="0"/>
         <v>5.2987868418287974E-2</v>
@@ -4627,7 +4627,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B48">
         <f t="shared" si="0"/>
         <v>5.8511840770746393E-2</v>
@@ -4637,7 +4637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B49">
         <f t="shared" si="0"/>
         <v>6.4319932607017835E-2</v>
@@ -4647,7 +4647,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B50">
         <f t="shared" si="0"/>
         <v>7.040232418023408E-2</v>
@@ -4657,7 +4657,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B51">
         <f t="shared" si="0"/>
         <v>7.6747182948336296E-2</v>
@@ -4667,7 +4667,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B52">
         <f t="shared" si="0"/>
         <v>8.3340699258080464E-2</v>
@@ -4677,7 +4677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B53">
         <f t="shared" si="0"/>
         <v>9.0167143898212704E-2</v>
@@ -4687,7 +4687,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B54">
         <f t="shared" si="0"/>
         <v>9.7208947972360321E-2</v>
@@ -4697,7 +4697,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B55">
         <f t="shared" si="0"/>
         <v>0.10444680519450757</v>
@@ -4707,7 +4707,7 @@
         <v>8.75</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B56">
         <f t="shared" si="0"/>
         <v>0.11185979633676199</v>
@@ -4717,7 +4717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B57">
         <f t="shared" si="0"/>
         <v>0.11942553516706651</v>
@@ -4727,7 +4727,7 @@
         <v>9.25</v>
       </c>
     </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B58">
         <f t="shared" si="0"/>
         <v>0.12712033481123883</v>
@@ -4737,7 +4737,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B59">
         <f t="shared" si="0"/>
         <v>0.13491939306780171</v>
@@ -4747,7 +4747,7 @@
         <v>9.75</v>
       </c>
     </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B60">
         <f t="shared" si="0"/>
         <v>0.14279699480482452</v>
@@ -4757,7 +4757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B61">
         <f t="shared" si="0"/>
         <v>0.15072672918526989</v>
@@ -4767,7 +4767,7 @@
         <v>10.25</v>
       </c>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B62">
         <f t="shared" si="0"/>
         <v>0.15868171911122922</v>
@@ -4777,7 +4777,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B63">
         <f t="shared" si="0"/>
         <v>0.16663485995800573</v>
@@ -4787,7 +4787,7 @@
         <v>10.75</v>
       </c>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B64">
         <f t="shared" si="0"/>
         <v>0.17455906439599175</v>
@@ -4797,7 +4797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B65">
         <f t="shared" si="0"/>
         <v>0.18242750988073522</v>
@@ -4807,7 +4807,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B66">
         <f t="shared" si="0"/>
         <v>0.19021388523755758</v>
@@ -4817,7 +4817,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B67">
         <f t="shared" si="0"/>
         <v>0.19789263268329291</v>
@@ -4827,7 +4827,7 @@
         <v>11.75</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B68">
         <f t="shared" si="0"/>
         <v>0.20543918161928124</v>
@@ -4837,7 +4837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B69">
         <f t="shared" si="0"/>
         <v>0.21283017059990736</v>
@@ -4847,7 +4847,7 @@
         <v>12.25</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B70">
         <f t="shared" si="0"/>
         <v>0.22004365403087262</v>
@@ -4857,7 +4857,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B71">
         <f t="shared" si="0"/>
         <v>0.22705929037995962</v>
@@ -4867,7 +4867,7 @@
         <v>12.75</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B72">
         <f t="shared" si="0"/>
         <v>0.23385850898689628</v>
@@ -4877,7 +4877,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B73">
         <f t="shared" si="0"/>
         <v>0.24042465293238419</v>
@@ -4887,7 +4887,7 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B74">
         <f t="shared" si="0"/>
         <v>0.2467430958615193</v>
@@ -4897,7 +4897,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B75">
         <f t="shared" si="0"/>
         <v>0.25280133114377951</v>
@@ -4907,7 +4907,7 @@
         <v>13.75</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B76">
         <f t="shared" si="0"/>
         <v>0.2585890322787715</v>
@@ -4917,7 +4917,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B77">
         <f t="shared" si="0"/>
         <v>0.26409808401086282</v>
@@ -4927,7 +4927,7 @@
         <v>14.25</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B78">
         <f t="shared" si="0"/>
         <v>0.26932258418246974</v>
@@ -4937,7 +4937,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B79">
         <f t="shared" si="0"/>
         <v>0.27425881692032672</v>
@@ -4947,7 +4947,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B80">
         <f t="shared" si="0"/>
         <v>0.2789051982966137</v>
@@ -4957,7 +4957,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B81">
         <f t="shared" si="0"/>
         <v>0.28326219612285092</v>
@@ -4967,7 +4967,7 @@
         <v>15.25</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B82">
         <f t="shared" si="0"/>
         <v>0.2873322260053523</v>
@@ -4977,7 +4977,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B83">
         <f t="shared" si="0"/>
         <v>0.29111952620450759</v>
@@ -4987,7 +4987,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B84">
         <f t="shared" si="0"/>
         <v>0.29463001418577178</v>
@@ -4997,7 +4997,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B85">
         <f t="shared" ref="B85:B121" si="2">(1-EXP(-((C85/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
         <v>0.29787112801967686</v>
@@ -5007,7 +5007,7 @@
         <v>16.25</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B86">
         <f t="shared" si="2"/>
         <v>0.30085165597558955</v>
@@ -5017,7 +5017,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B87">
         <f t="shared" si="2"/>
         <v>0.30358155775609158</v>
@@ -5027,7 +5027,7 @@
         <v>16.75</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B88">
         <f t="shared" si="2"/>
         <v>0.30607178083525383</v>
@@ -5037,7 +5037,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B89">
         <f t="shared" si="2"/>
         <v>0.30833407529690587</v>
@@ -5047,7 +5047,7 @@
         <v>17.25</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B90">
         <f t="shared" si="2"/>
         <v>0.31038081042304033</v>
@@ -5057,7 +5057,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B91">
         <f t="shared" si="2"/>
         <v>0.31222479606484704</v>
@@ -5067,7 +5067,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B92">
         <f t="shared" si="2"/>
         <v>0.31387911154870857</v>
@@ -5077,7 +5077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B93">
         <f t="shared" si="2"/>
         <v>0.31535694453758484</v>
@@ -5087,7 +5087,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B94">
         <f t="shared" si="2"/>
         <v>0.31667144189658553</v>
@@ -5097,7 +5097,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B95">
         <f t="shared" si="2"/>
         <v>0.3178355742128724</v>
@@ -5107,7 +5107,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96">
         <f t="shared" si="2"/>
         <v>0.31886201520731511</v>
@@ -5117,7 +5117,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B97">
         <f t="shared" si="2"/>
         <v>0.31976303686122226</v>
@@ -5127,7 +5127,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B98">
         <f t="shared" si="2"/>
         <v>0.32055042067798994</v>
@@ -5137,7 +5137,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B99">
         <f t="shared" si="2"/>
         <v>0.32123538511752886</v>
@@ -5147,7 +5147,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B100">
         <f t="shared" si="2"/>
         <v>0.32182852889030422</v>
@@ -5157,7 +5157,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B101">
         <f t="shared" si="2"/>
         <v>0.32233978948549169</v>
@@ -5167,7 +5167,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B102">
         <f t="shared" si="2"/>
         <v>0.32277841604000762</v>
@@ -5177,7 +5177,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B103">
         <f t="shared" si="2"/>
         <v>0.32315295543592437</v>
@@ -5187,7 +5187,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B104">
         <f t="shared" si="2"/>
         <v>0.32347125034502283</v>
@@ -5197,7 +5197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B105">
         <f t="shared" si="2"/>
         <v>0.32374044782105788</v>
@@ -5207,7 +5207,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B106">
         <f t="shared" si="2"/>
         <v>0.32396701697112512</v>
@@ -5217,7 +5217,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B107">
         <f t="shared" si="2"/>
         <v>0.32415677421421263</v>
@@ -5227,7 +5227,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B108">
         <f t="shared" si="2"/>
         <v>0.32431491465326501</v>
@@ -5237,7 +5237,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B109">
         <f t="shared" si="2"/>
         <v>0.32444604814158295</v>
@@ -5247,7 +5247,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B110">
         <f t="shared" si="2"/>
         <v>0.3245542387092018</v>
@@ -5257,7 +5257,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B111">
         <f t="shared" si="2"/>
         <v>0.32464304612372757</v>
@@ -5267,7 +5267,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B112">
         <f t="shared" si="2"/>
         <v>0.32471556848661476</v>
@@ -5277,7 +5277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B113">
         <f t="shared" si="2"/>
         <v>0.32477448490384953</v>
@@ -5287,7 +5287,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B114">
         <f t="shared" si="2"/>
         <v>0.32482209741368234</v>
@@ -5297,7 +5297,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B115">
         <f t="shared" si="2"/>
         <v>0.32486037149823072</v>
@@ -5307,7 +5307,7 @@
         <v>23.75</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B116">
         <f t="shared" si="2"/>
         <v>0.3248909746459317</v>
@@ -5317,7 +5317,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B117">
         <f t="shared" si="2"/>
         <v>0.32491531256425021</v>
@@ -5327,7 +5327,7 @@
         <v>24.25</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B118">
         <f t="shared" si="2"/>
         <v>0.32493456276384014</v>
@@ -5337,7 +5337,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B119">
         <f t="shared" si="2"/>
         <v>0.32494970534441392</v>
@@ -5347,7 +5347,7 @@
         <v>24.75</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B120">
         <f t="shared" si="2"/>
         <v>0.32496155090760193</v>
@@ -5357,7 +5357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B121">
         <f t="shared" si="2"/>
         <v>0.32497076560245858</v>
@@ -5379,13 +5379,13 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:CE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:83" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:83" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -6061,17 +6061,17 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
@@ -6089,108 +6089,111 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AF25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1">
+        <v>2020</v>
+      </c>
+      <c r="C1">
         <v>2021</v>
       </c>
-      <c r="C1">
+      <c r="D1">
         <v>2022</v>
       </c>
-      <c r="D1">
+      <c r="E1">
         <v>2023</v>
       </c>
-      <c r="E1">
+      <c r="F1">
         <v>2024</v>
       </c>
-      <c r="F1">
+      <c r="G1">
         <v>2025</v>
       </c>
-      <c r="G1">
+      <c r="H1">
         <v>2026</v>
       </c>
-      <c r="H1">
+      <c r="I1">
         <v>2027</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2028</v>
       </c>
-      <c r="J1">
+      <c r="K1">
         <v>2029</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>2030</v>
       </c>
-      <c r="L1">
+      <c r="M1">
         <v>2031</v>
       </c>
-      <c r="M1">
+      <c r="N1">
         <v>2032</v>
       </c>
-      <c r="N1">
+      <c r="O1">
         <v>2033</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <v>2034</v>
       </c>
-      <c r="P1">
+      <c r="Q1">
         <v>2035</v>
       </c>
-      <c r="Q1">
+      <c r="R1">
         <v>2036</v>
       </c>
-      <c r="R1">
+      <c r="S1">
         <v>2037</v>
       </c>
-      <c r="S1">
+      <c r="T1">
         <v>2038</v>
       </c>
-      <c r="T1">
+      <c r="U1">
         <v>2039</v>
       </c>
-      <c r="U1">
+      <c r="V1">
         <v>2040</v>
       </c>
-      <c r="V1">
+      <c r="W1">
         <v>2041</v>
       </c>
-      <c r="W1">
+      <c r="X1">
         <v>2042</v>
       </c>
-      <c r="X1">
+      <c r="Y1">
         <v>2043</v>
       </c>
-      <c r="Y1">
+      <c r="Z1">
         <v>2044</v>
       </c>
-      <c r="Z1">
+      <c r="AA1">
         <v>2045</v>
       </c>
-      <c r="AA1">
+      <c r="AB1">
         <v>2046</v>
       </c>
-      <c r="AB1">
+      <c r="AC1">
         <v>2047</v>
       </c>
-      <c r="AC1">
+      <c r="AD1">
         <v>2048</v>
       </c>
-      <c r="AD1">
+      <c r="AE1">
         <v>2049</v>
       </c>
-      <c r="AE1">
+      <c r="AF1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6284,8 +6287,11 @@
       <c r="AE2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6379,8 +6385,11 @@
       <c r="AE3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6474,8 +6483,11 @@
       <c r="AE4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6569,8 +6581,11 @@
       <c r="AE5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6664,8 +6679,11 @@
       <c r="AE6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -6759,8 +6777,11 @@
       <c r="AE7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6854,8 +6875,11 @@
       <c r="AE8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6949,8 +6973,11 @@
       <c r="AE9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7044,8 +7071,11 @@
       <c r="AE10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -7139,8 +7169,11 @@
       <c r="AE11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7234,8 +7267,11 @@
       <c r="AE12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7329,8 +7365,11 @@
       <c r="AE13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -7424,8 +7463,11 @@
       <c r="AE14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7519,8 +7561,11 @@
       <c r="AE15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7614,8 +7659,11 @@
       <c r="AE16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -7709,8 +7757,11 @@
       <c r="AE17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -7804,8 +7855,11 @@
       <c r="AE18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -7899,8 +7953,11 @@
       <c r="AE19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -7994,8 +8051,11 @@
       <c r="AE20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8089,8 +8149,11 @@
       <c r="AE21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -8184,8 +8247,11 @@
       <c r="AE22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -8279,8 +8345,11 @@
       <c r="AE23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -8374,8 +8443,11 @@
       <c r="AE24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -8467,6 +8539,9 @@
         <v>1</v>
       </c>
       <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
         <v>1</v>
       </c>
     </row>
@@ -8476,6 +8551,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -8619,15 +8703,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -8635,13 +8710,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4F2B5D9-2D55-40EB-8A9A-E5CF94C2AF63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B77D7DB8-4901-43F6-AAAE-109C28C1C1FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B77D7DB8-4901-43F6-AAAE-109C28C1C1FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4F2B5D9-2D55-40EB-8A9A-E5CF94C2AF63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D626CF-1FA7-4237-B356-1814AAA3B8F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D626CF-1FA7-4237-B356-1814AAA3B8F0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>